--- a/Calificaciones 2025-2026/Segundo Trimestre/N3_ENS_C_2.xlsx
+++ b/Calificaciones 2025-2026/Segundo Trimestre/N3_ENS_C_2.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GSE2GA\Documents\Personal\Tere Guerra\Meraki\Calificaciones 2025-2026\Segundo Trimestre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559E4425-1F1C-4597-A77E-4B944BCDCA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8F4BFD-FE34-4740-94EE-344548B6FFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-96" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-96" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificaciones" sheetId="3" r:id="rId1"/>
-    <sheet name="Libro 2" sheetId="4" r:id="rId2"/>
+    <sheet name="Libro" sheetId="4" r:id="rId2"/>
     <sheet name="Tareas" sheetId="1" r:id="rId3"/>
     <sheet name="Cuaderno" sheetId="6" r:id="rId4"/>
-    <sheet name="Incidencias" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="64">
   <si>
     <t>N3PRIMARIA 3°A</t>
   </si>
@@ -138,51 +137,15 @@
     <t xml:space="preserve">Temario </t>
   </si>
   <si>
-    <t xml:space="preserve">Revisión del Libro Páginas que debe. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisión del Cuaderno Lecciones no apuntadas. </t>
-  </si>
-  <si>
     <t>C4</t>
   </si>
   <si>
-    <t>Martes 25/11/2025                      ¿Qué es dialogar?</t>
-  </si>
-  <si>
     <t>C5</t>
   </si>
   <si>
-    <t>Miércoles 26/11/2025     Un trato digno para todos</t>
-  </si>
-  <si>
-    <t>Jueves 27/11/2025        ¿Qué es un fanzine?</t>
-  </si>
-  <si>
-    <t>Miércoles 3/12/2025       Una escuela segura</t>
-  </si>
-  <si>
-    <t>Jueves 4/12/2025             Plan de contingencia</t>
-  </si>
-  <si>
-    <t>Martes 9/12/2025              Nos preparamos ante los desastres</t>
-  </si>
-  <si>
-    <t>Miércoles 10/12/2025 ¡Todos somos iguales!</t>
-  </si>
-  <si>
     <t>C6</t>
   </si>
   <si>
-    <t>Jueves 11/12/2025       Roles de género</t>
-  </si>
-  <si>
-    <t>Martes 16/12/2025 Evaluación</t>
-  </si>
-  <si>
-    <t>Jueves 18/12/2025               Estereotipos de género</t>
-  </si>
-  <si>
     <t xml:space="preserve">Un mundo sin discriminación </t>
   </si>
   <si>
@@ -216,9 +179,6 @@
     <t>Igualdad en imágenes</t>
   </si>
   <si>
-    <t>Miércoles 26/11/2025             Un trato digno para todos</t>
-  </si>
-  <si>
     <t>Actividades</t>
   </si>
   <si>
@@ -232,6 +192,42 @@
   </si>
   <si>
     <t>Ética, naturaleza y sociedades</t>
+  </si>
+  <si>
+    <t>¿Qué es dialogar?</t>
+  </si>
+  <si>
+    <t>Un trato digno para todos</t>
+  </si>
+  <si>
+    <t>¿Qué es un fanzine?</t>
+  </si>
+  <si>
+    <t>Una escuela segura</t>
+  </si>
+  <si>
+    <t>Plan de contingencia</t>
+  </si>
+  <si>
+    <t>Nos preparamos ante los desastres</t>
+  </si>
+  <si>
+    <t>¡Todos somos iguales!</t>
+  </si>
+  <si>
+    <t>Roles de género</t>
+  </si>
+  <si>
+    <t>Evaluación</t>
+  </si>
+  <si>
+    <t>Estereotipos de género</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ¿Qué es dialogar?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Roles de género</t>
   </si>
 </sst>
 </file>
@@ -394,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -465,8 +461,6 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -482,6 +476,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -505,15 +502,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -832,22 +820,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32" t="s">
+      <c r="B2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
@@ -910,7 +898,7 @@
       <c r="K4" s="6">
         <v>0.1</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="29">
         <v>1</v>
       </c>
       <c r="M4" s="5"/>
@@ -957,20 +945,20 @@
       <c r="H6" s="10">
         <v>0</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="10" t="e">
         <f>Tareas!Q5</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="10">
-        <f>Cuaderno!O6*0.5 + 'Libro 2'!U7*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J6" s="10" t="e">
+        <f>Cuaderno!O6*0.5 + Libro!U7*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K6" s="10">
         <v>0</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="11" t="e">
         <f>E6*0.09 + F6*0.09 + G6*0.25 + H6*0.07 + I6*0.2 +J6*0.2 + K6*0.1</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="M6" s="5"/>
     </row>
@@ -996,20 +984,20 @@
       <c r="H7" s="10">
         <v>0</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="10" t="e">
         <f>Tareas!Q6</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <f>Cuaderno!O7*0.5 + 'Libro 2'!U8*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J7" s="10" t="e">
+        <f>Cuaderno!O7*0.5 + Libro!U8*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K7" s="10">
         <v>0</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="11" t="e">
         <f t="shared" ref="L7:L15" si="0">E7*0.09 + F7*0.09 + G7*0.25 + H7*0.07 + I7*0.2 +J7*0.2 + K7*0.1</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="M7" s="5"/>
     </row>
@@ -1035,20 +1023,20 @@
       <c r="H8" s="10">
         <v>0</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="10" t="e">
         <f>Tareas!Q7</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="10">
-        <f>Cuaderno!O8*0.5 + 'Libro 2'!U9*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J8" s="10" t="e">
+        <f>Cuaderno!O8*0.5 + Libro!U9*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K8" s="10">
         <v>0</v>
       </c>
-      <c r="L8" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="L8" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M8" s="5"/>
     </row>
@@ -1074,20 +1062,20 @@
       <c r="H9" s="10">
         <v>0</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="10" t="e">
         <f>Tareas!Q8</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="10">
-        <f>Cuaderno!O9*0.5 + 'Libro 2'!U10*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J9" s="10" t="e">
+        <f>Cuaderno!O9*0.5 + Libro!U10*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K9" s="10">
         <v>0</v>
       </c>
-      <c r="L9" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="L9" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M9" s="5"/>
     </row>
@@ -1113,20 +1101,20 @@
       <c r="H10" s="10">
         <v>0</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="10" t="e">
         <f>Tareas!Q9</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="10">
-        <f>Cuaderno!O10*0.5 + 'Libro 2'!U11*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J10" s="10" t="e">
+        <f>Cuaderno!O10*0.5 + Libro!U11*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K10" s="10">
         <v>0</v>
       </c>
-      <c r="L10" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="L10" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M10" s="5"/>
     </row>
@@ -1152,20 +1140,20 @@
       <c r="H11" s="10">
         <v>0</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="10" t="e">
         <f>Tareas!Q10</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="10">
-        <f>Cuaderno!O11*0.5 + 'Libro 2'!U12*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J11" s="10" t="e">
+        <f>Cuaderno!O11*0.5 + Libro!U12*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K11" s="10">
         <v>0</v>
       </c>
-      <c r="L11" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="L11" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M11" s="5"/>
     </row>
@@ -1191,20 +1179,20 @@
       <c r="H12" s="10">
         <v>0</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="10" t="e">
         <f>Tareas!Q11</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="10">
-        <f>Cuaderno!O12*0.5 + 'Libro 2'!U13*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J12" s="10" t="e">
+        <f>Cuaderno!O12*0.5 + Libro!U13*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K12" s="10">
         <v>0</v>
       </c>
-      <c r="L12" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="L12" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M12" s="5"/>
     </row>
@@ -1230,20 +1218,20 @@
       <c r="H13" s="10">
         <v>0</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="10" t="e">
         <f>Tareas!Q12</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="10">
-        <f>Cuaderno!O13*0.5 + 'Libro 2'!U14*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J13" s="10" t="e">
+        <f>Cuaderno!O13*0.5 + Libro!U14*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K13" s="10">
         <v>0</v>
       </c>
-      <c r="L13" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="L13" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M13" s="5"/>
     </row>
@@ -1269,20 +1257,20 @@
       <c r="H14" s="10">
         <v>0</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="10" t="e">
         <f>Tareas!Q13</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="10">
-        <f>Cuaderno!O14*0.5 + 'Libro 2'!U15*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J14" s="10" t="e">
+        <f>Cuaderno!O14*0.5 + Libro!U15*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K14" s="10">
         <v>0</v>
       </c>
-      <c r="L14" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="L14" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M14" s="5"/>
     </row>
@@ -1308,29 +1296,29 @@
       <c r="H15" s="10">
         <v>0</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="10" t="e">
         <f>Tareas!Q14</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="10">
-        <f>Cuaderno!O15*0.5 + 'Libro 2'!U16*0.5</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J15" s="10" t="e">
+        <f>Cuaderno!O15*0.5 + Libro!U16*0.5</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K15" s="10">
         <v>0</v>
       </c>
-      <c r="L15" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="L15" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="12">
         <f>AVERAGE(E6:E15)</f>
         <v>0</v>
@@ -1347,21 +1335,21 @@
         <f t="shared" ref="H16:L16" si="1">AVERAGE(H6:H15)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J16" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="K16" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="12" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="M16" s="13"/>
     </row>
@@ -1383,40 +1371,37 @@
   <cols>
     <col min="1" max="3" width="9.125" style="1"/>
     <col min="4" max="4" width="35.375" style="1" customWidth="1"/>
-    <col min="5" max="14" width="4.625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="7.75" style="1" customWidth="1"/>
-    <col min="19" max="20" width="4.625" style="1" customWidth="1"/>
+    <col min="5" max="14" width="4.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B2" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
+      <c r="B2" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
     </row>
     <row r="3" spans="2:21" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
@@ -1424,42 +1409,42 @@
       <c r="D3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="43"/>
-      <c r="G3" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="35"/>
-      <c r="I3" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="35"/>
-      <c r="K3" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="35"/>
-      <c r="M3" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="43"/>
+      <c r="E3" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="33"/>
+      <c r="G3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="34"/>
+      <c r="I3" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="34"/>
+      <c r="K3" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="34"/>
+      <c r="M3" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" s="33"/>
       <c r="O3" s="22" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="P3" s="22" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="T3" s="39"/>
+        <v>60</v>
+      </c>
+      <c r="S3" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="T3" s="38"/>
       <c r="U3" s="4" t="s">
         <v>10</v>
       </c>
@@ -1468,42 +1453,42 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="14"/>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="41"/>
+      <c r="G4" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="41"/>
+      <c r="I4" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="41"/>
+      <c r="K4" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="36"/>
+      <c r="M4" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="41"/>
+      <c r="O4" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="42"/>
-      <c r="I4" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="42"/>
-      <c r="K4" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" s="37"/>
-      <c r="M4" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" s="42"/>
-      <c r="O4" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="P4" s="16" t="s">
-        <v>44</v>
-      </c>
       <c r="Q4" s="14" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="R4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="S4" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="T4" s="41"/>
+      <c r="S4" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" s="40"/>
       <c r="U4" s="4"/>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.25">
@@ -1600,57 +1585,25 @@
       <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="21">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21">
-        <v>0</v>
-      </c>
-      <c r="G7" s="21">
-        <v>0</v>
-      </c>
-      <c r="H7" s="21">
-        <v>0</v>
-      </c>
-      <c r="I7" s="21">
-        <v>0</v>
-      </c>
-      <c r="J7" s="21">
-        <v>0</v>
-      </c>
-      <c r="K7" s="21">
-        <v>0</v>
-      </c>
-      <c r="L7" s="21">
-        <v>0</v>
-      </c>
-      <c r="M7" s="21">
-        <v>0</v>
-      </c>
-      <c r="N7" s="21">
-        <v>0</v>
-      </c>
-      <c r="O7" s="21">
-        <v>0</v>
-      </c>
-      <c r="P7" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="21">
-        <v>0</v>
-      </c>
-      <c r="R7" s="21">
-        <v>0</v>
-      </c>
-      <c r="S7" s="21">
-        <v>0</v>
-      </c>
-      <c r="T7" s="21">
-        <v>0</v>
-      </c>
-      <c r="U7" s="25">
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="25" t="e">
         <f t="shared" ref="U7:U16" si="0">AVERAGE(E7:T7)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.25">
@@ -1663,57 +1616,25 @@
       <c r="D8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="21">
-        <v>0</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0</v>
-      </c>
-      <c r="I8" s="21">
-        <v>0</v>
-      </c>
-      <c r="J8" s="21">
-        <v>0</v>
-      </c>
-      <c r="K8" s="21">
-        <v>0</v>
-      </c>
-      <c r="L8" s="21">
-        <v>0</v>
-      </c>
-      <c r="M8" s="21">
-        <v>0</v>
-      </c>
-      <c r="N8" s="21">
-        <v>0</v>
-      </c>
-      <c r="O8" s="21">
-        <v>0</v>
-      </c>
-      <c r="P8" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="21">
-        <v>0</v>
-      </c>
-      <c r="R8" s="21">
-        <v>0</v>
-      </c>
-      <c r="S8" s="21">
-        <v>0</v>
-      </c>
-      <c r="T8" s="21">
-        <v>0</v>
-      </c>
-      <c r="U8" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.25">
@@ -1726,57 +1647,25 @@
       <c r="D9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="21">
-        <v>0</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0</v>
-      </c>
-      <c r="I9" s="21">
-        <v>0</v>
-      </c>
-      <c r="J9" s="21">
-        <v>0</v>
-      </c>
-      <c r="K9" s="21">
-        <v>0</v>
-      </c>
-      <c r="L9" s="21">
-        <v>0</v>
-      </c>
-      <c r="M9" s="21">
-        <v>0</v>
-      </c>
-      <c r="N9" s="21">
-        <v>0</v>
-      </c>
-      <c r="O9" s="21">
-        <v>0</v>
-      </c>
-      <c r="P9" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="21">
-        <v>0</v>
-      </c>
-      <c r="R9" s="21">
-        <v>0</v>
-      </c>
-      <c r="S9" s="21">
-        <v>0</v>
-      </c>
-      <c r="T9" s="21">
-        <v>0</v>
-      </c>
-      <c r="U9" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.25">
@@ -1789,57 +1678,25 @@
       <c r="D10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="21">
-        <v>0</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0</v>
-      </c>
-      <c r="H10" s="21">
-        <v>0</v>
-      </c>
-      <c r="I10" s="21">
-        <v>0</v>
-      </c>
-      <c r="J10" s="21">
-        <v>0</v>
-      </c>
-      <c r="K10" s="21">
-        <v>0</v>
-      </c>
-      <c r="L10" s="21">
-        <v>0</v>
-      </c>
-      <c r="M10" s="21">
-        <v>0</v>
-      </c>
-      <c r="N10" s="21">
-        <v>0</v>
-      </c>
-      <c r="O10" s="21">
-        <v>0</v>
-      </c>
-      <c r="P10" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="21">
-        <v>0</v>
-      </c>
-      <c r="R10" s="21">
-        <v>0</v>
-      </c>
-      <c r="S10" s="21">
-        <v>0</v>
-      </c>
-      <c r="T10" s="21">
-        <v>0</v>
-      </c>
-      <c r="U10" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.25">
@@ -1852,57 +1709,25 @@
       <c r="D11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="21">
-        <v>0</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0</v>
-      </c>
-      <c r="G11" s="21">
-        <v>0</v>
-      </c>
-      <c r="H11" s="21">
-        <v>0</v>
-      </c>
-      <c r="I11" s="21">
-        <v>0</v>
-      </c>
-      <c r="J11" s="21">
-        <v>0</v>
-      </c>
-      <c r="K11" s="21">
-        <v>0</v>
-      </c>
-      <c r="L11" s="21">
-        <v>0</v>
-      </c>
-      <c r="M11" s="21">
-        <v>0</v>
-      </c>
-      <c r="N11" s="21">
-        <v>0</v>
-      </c>
-      <c r="O11" s="21">
-        <v>0</v>
-      </c>
-      <c r="P11" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="21">
-        <v>0</v>
-      </c>
-      <c r="R11" s="21">
-        <v>0</v>
-      </c>
-      <c r="S11" s="21">
-        <v>0</v>
-      </c>
-      <c r="T11" s="21">
-        <v>0</v>
-      </c>
-      <c r="U11" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.25">
@@ -1915,57 +1740,25 @@
       <c r="D12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="21">
-        <v>0</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0</v>
-      </c>
-      <c r="H12" s="21">
-        <v>0</v>
-      </c>
-      <c r="I12" s="21">
-        <v>0</v>
-      </c>
-      <c r="J12" s="21">
-        <v>0</v>
-      </c>
-      <c r="K12" s="21">
-        <v>0</v>
-      </c>
-      <c r="L12" s="21">
-        <v>0</v>
-      </c>
-      <c r="M12" s="21">
-        <v>0</v>
-      </c>
-      <c r="N12" s="21">
-        <v>0</v>
-      </c>
-      <c r="O12" s="21">
-        <v>0</v>
-      </c>
-      <c r="P12" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="21">
-        <v>0</v>
-      </c>
-      <c r="R12" s="21">
-        <v>0</v>
-      </c>
-      <c r="S12" s="21">
-        <v>0</v>
-      </c>
-      <c r="T12" s="21">
-        <v>0</v>
-      </c>
-      <c r="U12" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.25">
@@ -1978,57 +1771,25 @@
       <c r="D13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="21">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0</v>
-      </c>
-      <c r="I13" s="21">
-        <v>0</v>
-      </c>
-      <c r="J13" s="21">
-        <v>0</v>
-      </c>
-      <c r="K13" s="21">
-        <v>0</v>
-      </c>
-      <c r="L13" s="21">
-        <v>0</v>
-      </c>
-      <c r="M13" s="21">
-        <v>0</v>
-      </c>
-      <c r="N13" s="21">
-        <v>0</v>
-      </c>
-      <c r="O13" s="21">
-        <v>0</v>
-      </c>
-      <c r="P13" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="21">
-        <v>0</v>
-      </c>
-      <c r="R13" s="21">
-        <v>0</v>
-      </c>
-      <c r="S13" s="21">
-        <v>0</v>
-      </c>
-      <c r="T13" s="21">
-        <v>0</v>
-      </c>
-      <c r="U13" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.25">
@@ -2041,57 +1802,25 @@
       <c r="D14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="21">
-        <v>0</v>
-      </c>
-      <c r="F14" s="21">
-        <v>0</v>
-      </c>
-      <c r="G14" s="21">
-        <v>0</v>
-      </c>
-      <c r="H14" s="21">
-        <v>0</v>
-      </c>
-      <c r="I14" s="21">
-        <v>0</v>
-      </c>
-      <c r="J14" s="21">
-        <v>0</v>
-      </c>
-      <c r="K14" s="21">
-        <v>0</v>
-      </c>
-      <c r="L14" s="21">
-        <v>0</v>
-      </c>
-      <c r="M14" s="21">
-        <v>0</v>
-      </c>
-      <c r="N14" s="21">
-        <v>0</v>
-      </c>
-      <c r="O14" s="21">
-        <v>0</v>
-      </c>
-      <c r="P14" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="21">
-        <v>0</v>
-      </c>
-      <c r="R14" s="21">
-        <v>0</v>
-      </c>
-      <c r="S14" s="21">
-        <v>0</v>
-      </c>
-      <c r="T14" s="21">
-        <v>0</v>
-      </c>
-      <c r="U14" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.25">
@@ -2104,57 +1833,25 @@
       <c r="D15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="21">
-        <v>0</v>
-      </c>
-      <c r="F15" s="21">
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
-        <v>0</v>
-      </c>
-      <c r="H15" s="21">
-        <v>0</v>
-      </c>
-      <c r="I15" s="21">
-        <v>0</v>
-      </c>
-      <c r="J15" s="21">
-        <v>0</v>
-      </c>
-      <c r="K15" s="21">
-        <v>0</v>
-      </c>
-      <c r="L15" s="21">
-        <v>0</v>
-      </c>
-      <c r="M15" s="21">
-        <v>0</v>
-      </c>
-      <c r="N15" s="21">
-        <v>0</v>
-      </c>
-      <c r="O15" s="21">
-        <v>0</v>
-      </c>
-      <c r="P15" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="21">
-        <v>0</v>
-      </c>
-      <c r="R15" s="21">
-        <v>0</v>
-      </c>
-      <c r="S15" s="21">
-        <v>0</v>
-      </c>
-      <c r="T15" s="21">
-        <v>0</v>
-      </c>
-      <c r="U15" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.25">
@@ -2167,61 +1864,36 @@
       <c r="D16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="21">
-        <v>0</v>
-      </c>
-      <c r="F16" s="21">
-        <v>0</v>
-      </c>
-      <c r="G16" s="21">
-        <v>0</v>
-      </c>
-      <c r="H16" s="21">
-        <v>0</v>
-      </c>
-      <c r="I16" s="21">
-        <v>0</v>
-      </c>
-      <c r="J16" s="21">
-        <v>0</v>
-      </c>
-      <c r="K16" s="21">
-        <v>0</v>
-      </c>
-      <c r="L16" s="21">
-        <v>0</v>
-      </c>
-      <c r="M16" s="21">
-        <v>0</v>
-      </c>
-      <c r="N16" s="21">
-        <v>0</v>
-      </c>
-      <c r="O16" s="21">
-        <v>0</v>
-      </c>
-      <c r="P16" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="21">
-        <v>0</v>
-      </c>
-      <c r="R16" s="21">
-        <v>0</v>
-      </c>
-      <c r="S16" s="21">
-        <v>0</v>
-      </c>
-      <c r="T16" s="21">
-        <v>0</v>
-      </c>
-      <c r="U16" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:U2"/>
     <mergeCell ref="E3:F3"/>
@@ -2229,13 +1901,6 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2259,26 +1924,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
@@ -2337,37 +2002,37 @@
         <v>16</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="L4" s="26" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M4" s="26" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="P4" s="26" t="s">
         <v>32</v>
@@ -2384,45 +2049,21 @@
       <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="27">
-        <v>0</v>
-      </c>
-      <c r="F5" s="27">
-        <v>0</v>
-      </c>
-      <c r="G5" s="27">
-        <v>0</v>
-      </c>
-      <c r="H5" s="27">
-        <v>0</v>
-      </c>
-      <c r="I5" s="27">
-        <v>0</v>
-      </c>
-      <c r="J5" s="27">
-        <v>0</v>
-      </c>
-      <c r="K5" s="27">
-        <v>0</v>
-      </c>
-      <c r="L5" s="27">
-        <v>0</v>
-      </c>
-      <c r="M5" s="27">
-        <v>0</v>
-      </c>
-      <c r="N5" s="27">
-        <v>0</v>
-      </c>
-      <c r="O5" s="27">
-        <v>0</v>
-      </c>
-      <c r="P5" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11">
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="11" t="e">
         <f t="shared" ref="Q5:Q14" si="0">AVERAGE(E5:P5)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
@@ -2435,45 +2076,21 @@
       <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="27">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27">
-        <v>0</v>
-      </c>
-      <c r="M6" s="27">
-        <v>0</v>
-      </c>
-      <c r="N6" s="27">
-        <v>0</v>
-      </c>
-      <c r="O6" s="27">
-        <v>0</v>
-      </c>
-      <c r="P6" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
@@ -2486,45 +2103,21 @@
       <c r="D7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="27">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27">
-        <v>0</v>
-      </c>
-      <c r="M7" s="27">
-        <v>0</v>
-      </c>
-      <c r="N7" s="27">
-        <v>0</v>
-      </c>
-      <c r="O7" s="27">
-        <v>0</v>
-      </c>
-      <c r="P7" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
@@ -2537,45 +2130,21 @@
       <c r="D8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="27">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27">
-        <v>0</v>
-      </c>
-      <c r="I8" s="27">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27">
-        <v>0</v>
-      </c>
-      <c r="K8" s="27">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27">
-        <v>0</v>
-      </c>
-      <c r="M8" s="27">
-        <v>0</v>
-      </c>
-      <c r="N8" s="27">
-        <v>0</v>
-      </c>
-      <c r="O8" s="27">
-        <v>0</v>
-      </c>
-      <c r="P8" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
@@ -2588,45 +2157,21 @@
       <c r="D9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="27">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27">
-        <v>0</v>
-      </c>
-      <c r="I9" s="27">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27">
-        <v>0</v>
-      </c>
-      <c r="K9" s="27">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27">
-        <v>0</v>
-      </c>
-      <c r="M9" s="27">
-        <v>0</v>
-      </c>
-      <c r="N9" s="27">
-        <v>0</v>
-      </c>
-      <c r="O9" s="27">
-        <v>0</v>
-      </c>
-      <c r="P9" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
@@ -2639,45 +2184,21 @@
       <c r="D10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="27">
-        <v>0</v>
-      </c>
-      <c r="F10" s="27">
-        <v>0</v>
-      </c>
-      <c r="G10" s="27">
-        <v>0</v>
-      </c>
-      <c r="H10" s="27">
-        <v>0</v>
-      </c>
-      <c r="I10" s="27">
-        <v>0</v>
-      </c>
-      <c r="J10" s="27">
-        <v>0</v>
-      </c>
-      <c r="K10" s="27">
-        <v>0</v>
-      </c>
-      <c r="L10" s="27">
-        <v>0</v>
-      </c>
-      <c r="M10" s="27">
-        <v>0</v>
-      </c>
-      <c r="N10" s="27">
-        <v>0</v>
-      </c>
-      <c r="O10" s="27">
-        <v>0</v>
-      </c>
-      <c r="P10" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
@@ -2690,45 +2211,21 @@
       <c r="D11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="27">
-        <v>0</v>
-      </c>
-      <c r="F11" s="27">
-        <v>0</v>
-      </c>
-      <c r="G11" s="27">
-        <v>0</v>
-      </c>
-      <c r="H11" s="27">
-        <v>0</v>
-      </c>
-      <c r="I11" s="27">
-        <v>0</v>
-      </c>
-      <c r="J11" s="27">
-        <v>0</v>
-      </c>
-      <c r="K11" s="27">
-        <v>0</v>
-      </c>
-      <c r="L11" s="27">
-        <v>0</v>
-      </c>
-      <c r="M11" s="27">
-        <v>0</v>
-      </c>
-      <c r="N11" s="27">
-        <v>0</v>
-      </c>
-      <c r="O11" s="27">
-        <v>0</v>
-      </c>
-      <c r="P11" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
@@ -2741,45 +2238,21 @@
       <c r="D12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="27">
-        <v>0</v>
-      </c>
-      <c r="F12" s="27">
-        <v>0</v>
-      </c>
-      <c r="G12" s="27">
-        <v>0</v>
-      </c>
-      <c r="H12" s="27">
-        <v>0</v>
-      </c>
-      <c r="I12" s="27">
-        <v>0</v>
-      </c>
-      <c r="J12" s="27">
-        <v>0</v>
-      </c>
-      <c r="K12" s="27">
-        <v>0</v>
-      </c>
-      <c r="L12" s="27">
-        <v>0</v>
-      </c>
-      <c r="M12" s="27">
-        <v>0</v>
-      </c>
-      <c r="N12" s="27">
-        <v>0</v>
-      </c>
-      <c r="O12" s="27">
-        <v>0</v>
-      </c>
-      <c r="P12" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
@@ -2792,45 +2265,21 @@
       <c r="D13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="27">
-        <v>0</v>
-      </c>
-      <c r="F13" s="27">
-        <v>0</v>
-      </c>
-      <c r="G13" s="27">
-        <v>0</v>
-      </c>
-      <c r="H13" s="27">
-        <v>0</v>
-      </c>
-      <c r="I13" s="27">
-        <v>0</v>
-      </c>
-      <c r="J13" s="27">
-        <v>0</v>
-      </c>
-      <c r="K13" s="27">
-        <v>0</v>
-      </c>
-      <c r="L13" s="27">
-        <v>0</v>
-      </c>
-      <c r="M13" s="27">
-        <v>0</v>
-      </c>
-      <c r="N13" s="27">
-        <v>0</v>
-      </c>
-      <c r="O13" s="27">
-        <v>0</v>
-      </c>
-      <c r="P13" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
@@ -2843,45 +2292,21 @@
       <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="27">
-        <v>0</v>
-      </c>
-      <c r="F14" s="27">
-        <v>0</v>
-      </c>
-      <c r="G14" s="27">
-        <v>0</v>
-      </c>
-      <c r="H14" s="27">
-        <v>0</v>
-      </c>
-      <c r="I14" s="27">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27">
-        <v>0</v>
-      </c>
-      <c r="K14" s="27">
-        <v>0</v>
-      </c>
-      <c r="L14" s="27">
-        <v>0</v>
-      </c>
-      <c r="M14" s="27">
-        <v>0</v>
-      </c>
-      <c r="N14" s="27">
-        <v>0</v>
-      </c>
-      <c r="O14" s="27">
-        <v>0</v>
-      </c>
-      <c r="P14" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="R14" s="1">
         <v>4</v>
@@ -2904,67 +2329,67 @@
   <cols>
     <col min="1" max="3" width="9.125" style="1"/>
     <col min="4" max="4" width="35.375" style="1" customWidth="1"/>
-    <col min="5" max="9" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
+      <c r="B2" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
     </row>
     <row r="3" spans="2:15" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="28" t="s">
         <v>61</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3" s="30" t="s">
-        <v>47</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>10</v>
@@ -2974,7 +2399,7 @@
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E4" s="18">
         <v>1</v>
@@ -3040,39 +2465,19 @@
       <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="21">
-        <v>0</v>
-      </c>
-      <c r="F6" s="21">
-        <v>0</v>
-      </c>
-      <c r="G6" s="21">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>0</v>
-      </c>
-      <c r="I6" s="21">
-        <v>0</v>
-      </c>
-      <c r="J6" s="21">
-        <v>0</v>
-      </c>
-      <c r="K6" s="21">
-        <v>0</v>
-      </c>
-      <c r="L6" s="21">
-        <v>0</v>
-      </c>
-      <c r="M6" s="21">
-        <v>0</v>
-      </c>
-      <c r="N6" s="21">
-        <v>0</v>
-      </c>
-      <c r="O6" s="25">
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="25" t="e">
         <f t="shared" ref="O6:O15" si="0">AVERAGE(E6:N6)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
@@ -3085,39 +2490,19 @@
       <c r="D7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="21">
-        <v>0</v>
-      </c>
-      <c r="F7" s="21">
-        <v>0</v>
-      </c>
-      <c r="G7" s="21">
-        <v>0</v>
-      </c>
-      <c r="H7" s="21">
-        <v>0</v>
-      </c>
-      <c r="I7" s="21">
-        <v>0</v>
-      </c>
-      <c r="J7" s="21">
-        <v>0</v>
-      </c>
-      <c r="K7" s="21">
-        <v>0</v>
-      </c>
-      <c r="L7" s="21">
-        <v>0</v>
-      </c>
-      <c r="M7" s="21">
-        <v>0</v>
-      </c>
-      <c r="N7" s="21">
-        <v>0</v>
-      </c>
-      <c r="O7" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
@@ -3130,39 +2515,19 @@
       <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="21">
-        <v>0</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0</v>
-      </c>
-      <c r="I8" s="21">
-        <v>0</v>
-      </c>
-      <c r="J8" s="21">
-        <v>0</v>
-      </c>
-      <c r="K8" s="21">
-        <v>0</v>
-      </c>
-      <c r="L8" s="21">
-        <v>0</v>
-      </c>
-      <c r="M8" s="21">
-        <v>0</v>
-      </c>
-      <c r="N8" s="21">
-        <v>0</v>
-      </c>
-      <c r="O8" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
@@ -3175,39 +2540,19 @@
       <c r="D9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="21">
-        <v>0</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0</v>
-      </c>
-      <c r="I9" s="21">
-        <v>0</v>
-      </c>
-      <c r="J9" s="21">
-        <v>0</v>
-      </c>
-      <c r="K9" s="21">
-        <v>0</v>
-      </c>
-      <c r="L9" s="21">
-        <v>0</v>
-      </c>
-      <c r="M9" s="21">
-        <v>0</v>
-      </c>
-      <c r="N9" s="21">
-        <v>0</v>
-      </c>
-      <c r="O9" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
@@ -3220,39 +2565,19 @@
       <c r="D10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="21">
-        <v>0</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0</v>
-      </c>
-      <c r="H10" s="21">
-        <v>0</v>
-      </c>
-      <c r="I10" s="21">
-        <v>0</v>
-      </c>
-      <c r="J10" s="21">
-        <v>0</v>
-      </c>
-      <c r="K10" s="21">
-        <v>0</v>
-      </c>
-      <c r="L10" s="21">
-        <v>0</v>
-      </c>
-      <c r="M10" s="21">
-        <v>0</v>
-      </c>
-      <c r="N10" s="21">
-        <v>0</v>
-      </c>
-      <c r="O10" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
@@ -3265,39 +2590,19 @@
       <c r="D11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="21">
-        <v>0</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0</v>
-      </c>
-      <c r="G11" s="21">
-        <v>0</v>
-      </c>
-      <c r="H11" s="21">
-        <v>0</v>
-      </c>
-      <c r="I11" s="21">
-        <v>0</v>
-      </c>
-      <c r="J11" s="21">
-        <v>0</v>
-      </c>
-      <c r="K11" s="21">
-        <v>0</v>
-      </c>
-      <c r="L11" s="21">
-        <v>0</v>
-      </c>
-      <c r="M11" s="21">
-        <v>0</v>
-      </c>
-      <c r="N11" s="21">
-        <v>0</v>
-      </c>
-      <c r="O11" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
@@ -3310,39 +2615,19 @@
       <c r="D12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="21">
-        <v>0</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0</v>
-      </c>
-      <c r="H12" s="21">
-        <v>0</v>
-      </c>
-      <c r="I12" s="21">
-        <v>0</v>
-      </c>
-      <c r="J12" s="21">
-        <v>0</v>
-      </c>
-      <c r="K12" s="21">
-        <v>0</v>
-      </c>
-      <c r="L12" s="21">
-        <v>0</v>
-      </c>
-      <c r="M12" s="21">
-        <v>0</v>
-      </c>
-      <c r="N12" s="21">
-        <v>0</v>
-      </c>
-      <c r="O12" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
@@ -3355,39 +2640,19 @@
       <c r="D13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="21">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0</v>
-      </c>
-      <c r="I13" s="21">
-        <v>0</v>
-      </c>
-      <c r="J13" s="21">
-        <v>0</v>
-      </c>
-      <c r="K13" s="21">
-        <v>0</v>
-      </c>
-      <c r="L13" s="21">
-        <v>0</v>
-      </c>
-      <c r="M13" s="21">
-        <v>0</v>
-      </c>
-      <c r="N13" s="21">
-        <v>0</v>
-      </c>
-      <c r="O13" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
@@ -3400,39 +2665,19 @@
       <c r="D14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="21">
-        <v>0</v>
-      </c>
-      <c r="F14" s="21">
-        <v>0</v>
-      </c>
-      <c r="G14" s="21">
-        <v>0</v>
-      </c>
-      <c r="H14" s="21">
-        <v>0</v>
-      </c>
-      <c r="I14" s="21">
-        <v>0</v>
-      </c>
-      <c r="J14" s="21">
-        <v>0</v>
-      </c>
-      <c r="K14" s="21">
-        <v>0</v>
-      </c>
-      <c r="L14" s="21">
-        <v>0</v>
-      </c>
-      <c r="M14" s="21">
-        <v>0</v>
-      </c>
-      <c r="N14" s="21">
-        <v>0</v>
-      </c>
-      <c r="O14" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
@@ -3445,39 +2690,19 @@
       <c r="D15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="21">
-        <v>0</v>
-      </c>
-      <c r="F15" s="21">
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
-        <v>0</v>
-      </c>
-      <c r="H15" s="21">
-        <v>0</v>
-      </c>
-      <c r="I15" s="21">
-        <v>0</v>
-      </c>
-      <c r="J15" s="21">
-        <v>0</v>
-      </c>
-      <c r="K15" s="21">
-        <v>0</v>
-      </c>
-      <c r="L15" s="21">
-        <v>0</v>
-      </c>
-      <c r="M15" s="21">
-        <v>0</v>
-      </c>
-      <c r="N15" s="21">
-        <v>0</v>
-      </c>
-      <c r="O15" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
@@ -3487,190 +2712,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="32.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="39.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="47.25" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="45"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="9">
-        <v>1</v>
-      </c>
-      <c r="C5" s="9">
-        <v>979</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="9">
-        <v>2</v>
-      </c>
-      <c r="C6" s="9">
-        <v>1133</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="9">
-        <v>3</v>
-      </c>
-      <c r="C7" s="9">
-        <v>1235</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="9">
-        <v>4</v>
-      </c>
-      <c r="C8" s="9">
-        <v>986</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="9">
-        <v>5</v>
-      </c>
-      <c r="C9" s="9">
-        <v>1105</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="9">
-        <v>6</v>
-      </c>
-      <c r="C10" s="9">
-        <v>944</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="9">
-        <v>7</v>
-      </c>
-      <c r="C11" s="9">
-        <v>1021</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="9">
-        <v>8</v>
-      </c>
-      <c r="C12" s="9">
-        <v>1219</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="9">
-        <v>9</v>
-      </c>
-      <c r="C13" s="9">
-        <v>1220</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="9">
-        <v>10</v>
-      </c>
-      <c r="C14" s="9">
-        <v>1278</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>